--- a/1/food/2026-01-22-sm.xlsx
+++ b/1/food/2026-01-22-sm.xlsx
@@ -1,163 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11400" windowHeight="5895"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="11400" windowHeight="5895" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" refMode="R1C1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList/>
-</comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>Школа</t>
-  </si>
-  <si>
-    <t>МБОУ «НОШ с.Зумсой»</t>
-  </si>
-  <si>
-    <t>Отд./корп</t>
-  </si>
-  <si>
-    <t>День</t>
-  </si>
-  <si>
-    <t>22.01.2026</t>
-  </si>
-  <si>
-    <t>Прием пищи</t>
-  </si>
-  <si>
-    <t>Раздел</t>
-  </si>
-  <si>
-    <t>№ рец.</t>
-  </si>
-  <si>
-    <t>Блюдо</t>
-  </si>
-  <si>
-    <t>Выход, г</t>
-  </si>
-  <si>
-    <t>Цена</t>
-  </si>
-  <si>
-    <t>Калорийность</t>
-  </si>
-  <si>
-    <t>Белки</t>
-  </si>
-  <si>
-    <t>Жиры</t>
-  </si>
-  <si>
-    <t>Углеводы</t>
-  </si>
-  <si>
-    <t>Завтрак</t>
-  </si>
-  <si>
-    <t>гор.блюдо</t>
-  </si>
-  <si>
-    <t>Котлета куриная</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Греча отварная №4,3</t>
-  </si>
-  <si>
-    <t>гор.напиток</t>
-  </si>
-  <si>
-    <t>459</t>
-  </si>
-  <si>
-    <t>Чай с лимоном №459</t>
-  </si>
-  <si>
-    <t>хлеб</t>
-  </si>
-  <si>
-    <t>Хлеб пшеничный</t>
-  </si>
-  <si>
-    <t>фрукты</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>Яблоко №338</t>
-  </si>
-  <si>
-    <t>Обед</t>
-  </si>
-  <si>
-    <t>закуска</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Салат из моркови с сухофруктами №24</t>
-  </si>
-  <si>
-    <t>1 блюдо</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Суп с фасолью №119</t>
-  </si>
-  <si>
-    <t>2 блюдо</t>
-  </si>
-  <si>
-    <t>291</t>
-  </si>
-  <si>
-    <t>Плов с курицей №291</t>
-  </si>
-  <si>
-    <t>гарнир</t>
-  </si>
-  <si>
-    <t>напиток</t>
-  </si>
-  <si>
-    <t>хлеб бел.</t>
-  </si>
-  <si>
-    <t>хлеб черн.</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="50" formatCode=""/>
-    <numFmt numFmtId="51" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -168,48 +27,39 @@
       <name val="Arial"/>
       <charset val="0"/>
       <family val="2"/>
-      <b val="false"/>
-      <i val="false"/>
-      <strike val="false"/>
+      <strike val="0"/>
       <sz val="8"/>
-      <u val="none"/>
     </font>
     <font>
       <name val="Calibri"/>
       <charset val="0"/>
       <family val="0"/>
-      <b val="false"/>
-      <i val="false"/>
-      <strike val="false"/>
+      <strike val="0"/>
       <sz val="11"/>
-      <u val="none"/>
     </font>
     <font>
       <name val="Calibri"/>
       <charset val="0"/>
       <family val="0"/>
-      <b val="false"/>
-      <i val="false"/>
-      <strike val="false"/>
+      <strike val="0"/>
       <sz val="1"/>
-      <u val="none"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2CB"/>
-        <bgColor auto="true"/>
+        <fgColor rgb="00FFF2CB"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -220,13 +70,13 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -234,38 +84,38 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -274,37 +124,37 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -312,77 +162,77 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
+      </top>
+      <bottom>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top/>
       <bottom/>
@@ -390,281 +240,697 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </left>
       <right style="medium">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="000000"/>
-      </bottom>
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
-    <xf numFmtId="0" fontId="0"/>
-    <xf numFmtId="0" fontId="0" applyAlignment="true">
+  <cellXfs count="44">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="5" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" borderId="6" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" borderId="8" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" borderId="9" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" borderId="10" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" wrapText="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="11" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="51" fontId="2" fillId="2" borderId="11" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="51" fontId="2" fillId="2" borderId="12" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" borderId="13" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="51" fontId="2" fillId="2" borderId="4" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="51" fontId="2" fillId="2" borderId="14" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" borderId="15" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
-    <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="J19"/>
-  <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="11.429" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" style="1" customWidth="true"/>
-    <col min="2" max="2" width="15.66796875" style="1" customWidth="true"/>
-    <col min="3" max="3" width="14.33203125" style="1" customWidth="true"/>
-    <col min="4" max="4" width="59.5" style="1" customWidth="true"/>
-    <col min="5" max="5" width="11.83203125" style="1" customWidth="true"/>
-    <col min="6" max="6" width="12.5" style="1" customWidth="true"/>
-    <col min="7" max="7" width="16.5" style="1" customWidth="true"/>
-    <col min="8" max="8" width="10.83203125" style="1" customWidth="true"/>
-    <col min="9" max="9" width="11.16796875" style="1" customWidth="true"/>
-    <col min="10" max="10" width="12.33203125" style="1" customWidth="true"/>
+    <col width="16.83203125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.66796875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="14.33203125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="59.5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11.83203125" customWidth="1" style="1" min="5" max="5"/>
+    <col width="12.5" customWidth="1" style="1" min="6" max="6"/>
+    <col width="16.5" customWidth="1" style="1" min="7" max="7"/>
+    <col width="10.83203125" customWidth="1" style="1" min="8" max="8"/>
+    <col width="11.16796875" customWidth="1" style="1" min="9" max="9"/>
+    <col width="12.33203125" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="true">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="e"/>
-      <c r="D1" s="3" t="e"/>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Школа</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>"МБОУ СОШ №1 с.Алхан-Кала"</t>
+        </is>
+      </c>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="39" t="n"/>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Отд./корп</t>
+        </is>
       </c>
       <c r="F1" s="9" t="e"/>
       <c r="G1" s="10" t="e"/>
-      <c r="I1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="true" s="1" customFormat="true">
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customFormat="1" customHeight="1" s="1">
       <c r="B2" s="12" t="e"/>
       <c r="C2" s="12" t="e"/>
       <c r="D2" s="12" t="e"/>
     </row>
-    <row r="3" ht="15" customHeight="true">
-      <c r="A3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="true">
-      <c r="A4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>16</v>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Прием пищи</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Раздел</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>№ рец.</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Блюдо</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Выход, г</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Калорийность</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>Белки</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Жиры</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Углеводы</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Завтрак</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>гор.блюдо</t>
+        </is>
       </c>
       <c r="C4" s="19" t="e"/>
-      <c r="D4" s="20" t="s">
-        <v>17</v>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
       </c>
       <c r="E4" s="21" t="n">
         <v>70</v>
@@ -675,26 +941,32 @@
       <c r="G4" s="21" t="n">
         <v>203</v>
       </c>
-      <c r="H4" s="23" t="n">
+      <c r="H4" s="40" t="n">
         <v>6.7</v>
       </c>
-      <c r="I4" s="23" t="n">
+      <c r="I4" s="40" t="n">
         <v>12.6</v>
       </c>
-      <c r="J4" s="24" t="n">
+      <c r="J4" s="41" t="n">
         <v>19.6</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="true">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="25" t="e"/>
-      <c r="B5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>19</v>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>гор.блюдо</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Греча отварная №4,3</t>
+        </is>
       </c>
       <c r="E5" s="28" t="n">
         <v>100</v>
@@ -705,26 +977,32 @@
       <c r="G5" s="28" t="n">
         <v>151</v>
       </c>
-      <c r="H5" s="30" t="n">
+      <c r="H5" s="42" t="n">
         <v>5.7</v>
       </c>
-      <c r="I5" s="30" t="n">
+      <c r="I5" s="42" t="n">
         <v>4.1</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="43" t="n">
         <v>25.8</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="true">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="25" t="e"/>
-      <c r="B6" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>22</v>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>гор.напиток</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
       </c>
       <c r="E6" s="28" t="n">
         <v>180</v>
@@ -736,21 +1014,25 @@
         <v>39</v>
       </c>
       <c r="H6" s="32" t="e"/>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="42" t="n">
         <v>0.1</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="43" t="n">
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="true">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="25" t="e"/>
-      <c r="B7" s="26" t="s">
-        <v>23</v>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>хлеб</t>
+        </is>
       </c>
       <c r="C7" s="27" t="e"/>
-      <c r="D7" s="26" t="s">
-        <v>24</v>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
       </c>
       <c r="E7" s="28" t="n">
         <v>50</v>
@@ -761,26 +1043,32 @@
       <c r="G7" s="28" t="n">
         <v>117</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="42" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" s="30" t="n">
+      <c r="I7" s="42" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="43" t="n">
         <v>24.1</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="true">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="25" t="e"/>
-      <c r="B8" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>27</v>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>фрукты</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Яблоко №338</t>
+        </is>
       </c>
       <c r="E8" s="28" t="n">
         <v>100</v>
@@ -791,17 +1079,17 @@
       <c r="G8" s="28" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="42" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="42" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="43" t="n">
         <v>16.8</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="true">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="25" t="e"/>
       <c r="B9" s="26" t="e"/>
       <c r="C9" s="27" t="e"/>
@@ -813,7 +1101,7 @@
       <c r="I9" s="32" t="e"/>
       <c r="J9" s="33" t="e"/>
     </row>
-    <row r="10" ht="15" customHeight="true">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="25" t="e"/>
       <c r="B10" s="26" t="e"/>
       <c r="C10" s="27" t="e"/>
@@ -825,18 +1113,26 @@
       <c r="I10" s="32" t="e"/>
       <c r="J10" s="33" t="e"/>
     </row>
-    <row r="11" ht="15" customHeight="true">
-      <c r="A11" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>31</v>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Обед</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>закуска</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Салат из моркови с сухофруктами №24</t>
+        </is>
       </c>
       <c r="E11" s="21" t="n">
         <v>80</v>
@@ -847,26 +1143,32 @@
       <c r="G11" s="21" t="n">
         <v>87</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="40" t="n">
         <v>0.8</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="40" t="n">
         <v>4.3</v>
       </c>
-      <c r="J11" s="24" t="n">
+      <c r="J11" s="41" t="n">
         <v>11.3</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="true">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="25" t="e"/>
-      <c r="B12" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>34</v>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>1 блюдо</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Суп с фасолью №119</t>
+        </is>
       </c>
       <c r="E12" s="28" t="n">
         <v>200</v>
@@ -877,26 +1179,32 @@
       <c r="G12" s="28" t="n">
         <v>241</v>
       </c>
-      <c r="H12" s="30" t="n">
+      <c r="H12" s="42" t="n">
         <v>5.7</v>
       </c>
-      <c r="I12" s="30" t="n">
+      <c r="I12" s="42" t="n">
         <v>19.4</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="43" t="n">
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="true">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="e"/>
-      <c r="B13" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>37</v>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>2 блюдо</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Плов с курицей №291</t>
+        </is>
       </c>
       <c r="E13" s="28" t="n">
         <v>120</v>
@@ -907,20 +1215,22 @@
       <c r="G13" s="28" t="n">
         <v>220</v>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="42" t="n">
         <v>13.6</v>
       </c>
-      <c r="I13" s="30" t="n">
+      <c r="I13" s="42" t="n">
         <v>8.4</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="43" t="n">
         <v>28.6</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="true">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="25" t="e"/>
-      <c r="B14" s="26" t="s">
-        <v>38</v>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>гарнир</t>
+        </is>
       </c>
       <c r="C14" s="27" t="e"/>
       <c r="D14" s="26" t="e"/>
@@ -931,16 +1241,22 @@
       <c r="I14" s="32" t="e"/>
       <c r="J14" s="33" t="e"/>
     </row>
-    <row r="15" ht="15" customHeight="true">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="25" t="e"/>
-      <c r="B15" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>22</v>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>напиток</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
       </c>
       <c r="E15" s="28" t="n">
         <v>200</v>
@@ -952,45 +1268,51 @@
         <v>39</v>
       </c>
       <c r="H15" s="32" t="e"/>
-      <c r="I15" s="30" t="n">
+      <c r="I15" s="42" t="n">
         <v>0.1</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="43" t="n">
         <v>9.5</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="true">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="25" t="e"/>
-      <c r="B16" s="26" t="s">
-        <v>40</v>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>хлеб бел.</t>
+        </is>
       </c>
       <c r="C16" s="27" t="e"/>
-      <c r="D16" s="26" t="s">
-        <v>24</v>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
       </c>
       <c r="E16" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="42" t="n">
         <v>7.2</v>
       </c>
       <c r="G16" s="28" t="n">
         <v>171</v>
       </c>
-      <c r="H16" s="30" t="n">
+      <c r="H16" s="42" t="n">
         <v>6.3</v>
       </c>
-      <c r="I16" s="30" t="n">
+      <c r="I16" s="42" t="n">
         <v>0.8</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="43" t="n">
         <v>38.6</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="true">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="25" t="e"/>
-      <c r="B17" s="26" t="s">
-        <v>41</v>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>хлеб черн.</t>
+        </is>
       </c>
       <c r="C17" s="27" t="e"/>
       <c r="D17" s="26" t="e"/>
@@ -1001,7 +1323,7 @@
       <c r="I17" s="32" t="e"/>
       <c r="J17" s="33" t="e"/>
     </row>
-    <row r="18" ht="15" customHeight="true">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="25" t="e"/>
       <c r="B18" s="26" t="e"/>
       <c r="C18" s="27" t="e"/>
@@ -1013,7 +1335,7 @@
       <c r="I18" s="32" t="e"/>
       <c r="J18" s="33" t="e"/>
     </row>
-    <row r="19" ht="15" customHeight="true">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="34" t="e"/>
       <c r="B19" s="35" t="e"/>
       <c r="C19" s="36" t="e"/>
@@ -1029,11 +1351,15 @@
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
-  <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>
-  <headerFooter alignWithMargins="true" scaleWithDoc="true"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <legacyDrawingHF r:id="rId5"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" scale="100" pageOrder="overThenDown" blackAndWhite="0"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>